--- a/src/configs/xlsx/agents/test_agents.xlsx
+++ b/src/configs/xlsx/agents/test_agents.xlsx
@@ -1,151 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solisservices-my.sharepoint.com/personal/t_d_atkinson_uu_nl/Documents/Documents/julia/TemporalOrganizationOfShortTermElectricityMarkets/src/configs/xlsx/agents/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="126" documentId="8_{F29EF3F7-20E7-4DD4-9D78-F542FA4C4C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C557595-2E4C-4FA1-A080-FFA771AFDDC5}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="15180" yWindow="-21600" windowWidth="19410" windowHeight="20985" xr2:uid="{1FA0DA74-D4EF-4506-932F-5F129A1E312C}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="15180" yWindow="-21600" windowWidth="19410" windowHeight="20985" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Generators" sheetId="1" r:id="rId1"/>
-    <sheet name="Demands" sheetId="2" r:id="rId2"/>
-    <sheet name="Storage" sheetId="3" r:id="rId3"/>
+    <sheet name="Generators" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Demands" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Storage" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="30">
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Bid Price</t>
-  </si>
-  <si>
-    <t>Ramp Rate</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Initial Quantity</t>
-  </si>
-  <si>
-    <t>Profile</t>
-  </si>
-  <si>
-    <t>Profile File</t>
-  </si>
-  <si>
-    <t>Emission Factor</t>
-  </si>
-  <si>
-    <t>Energy Capacity</t>
-  </si>
-  <si>
-    <t>Power Capacity</t>
-  </si>
-  <si>
-    <t>Efficiency</t>
-  </si>
-  <si>
-    <t>Initial SOC</t>
-  </si>
-  <si>
-    <t>End SOC</t>
-  </si>
-  <si>
-    <t>Base_D</t>
-  </si>
-  <si>
-    <t>Flex</t>
-  </si>
-  <si>
-    <t>[50, 50, 50, 50, 50, 50, 50, 50, 50]</t>
-  </si>
-  <si>
-    <t>Base</t>
-  </si>
-  <si>
-    <t>Dispatchable</t>
-  </si>
-  <si>
-    <t>Shoulder</t>
-  </si>
-  <si>
-    <t>Capacity</t>
-  </si>
-  <si>
-    <t>Peak</t>
-  </si>
-  <si>
-    <t>Variable</t>
-  </si>
-  <si>
-    <t>Wind</t>
-  </si>
-  <si>
-    <t>Solar</t>
-  </si>
-  <si>
-    <t>Profile Type</t>
-  </si>
-  <si>
-    <t>quantity</t>
-  </si>
-  <si>
-    <t>availability</t>
-  </si>
-  <si>
-    <t>input_data/wind-2026-uur-data.csv</t>
-  </si>
-  <si>
-    <t>input_data/zon-2026-uur-data.csv</t>
-  </si>
-  <si>
-    <t>input_data/electriciteitsmix-2026-uur-data.csv</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -164,21 +48,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -498,156 +441,208 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{797BB634-6813-4727-8565-3F3E0B9FC729}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col min="5" max="5" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="39.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col width="9.90625" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="13.453125" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="14.54296875" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="39.54296875" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="10.6328125" bestFit="1" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Bid Price</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Ramp Rate</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Initial Quantity</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Emission Factor</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Profile File</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Profile Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>3G_Base</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dispatchable</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>60</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3309</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G2" t="n">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>4G_Shoulder</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dispatchable</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>90</v>
+      </c>
+      <c r="D3" t="n">
+        <v>9523</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2">
-        <v>60</v>
-      </c>
-      <c r="D2">
-        <v>3309</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>100</v>
-      </c>
-      <c r="G2">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3">
-        <v>90</v>
-      </c>
-      <c r="D3">
-        <v>9523</v>
-      </c>
-      <c r="E3">
-        <v>6</v>
-      </c>
-      <c r="F3">
+      <c r="G3" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>5G_Peak</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dispatchable</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>120</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3738</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
         <v>0</v>
       </c>
-      <c r="G3">
+      <c r="G4" t="n">
         <v>420</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4">
-        <v>120</v>
-      </c>
-      <c r="D4">
-        <v>3738</v>
-      </c>
-      <c r="E4">
-        <v>12</v>
-      </c>
-      <c r="F4">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>6G_Wind</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>0</v>
       </c>
-      <c r="G4">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5">
+      <c r="D5" t="n">
+        <v>11036</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>input_data/wind-2026-uur-data.csv</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>availability</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>7G_Solar</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>0</v>
       </c>
-      <c r="D5">
-        <v>11036</v>
-      </c>
-      <c r="I5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>24700</v>
       </c>
-      <c r="I6" t="s">
-        <v>28</v>
-      </c>
-      <c r="J6" t="s">
-        <v>26</v>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>input_data/zon-2026-uur-data.csv</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>availability</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -656,54 +651,81 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2EDA3C1-D16B-4F0B-8ECC-ACF143CFF631}">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col min="3" max="3" width="33.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="41.26953125" bestFit="1" customWidth="1"/>
+    <col width="33.81640625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="41.26953125" bestFit="1" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Bid Price</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Profile File</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Profile Type</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Quantity Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1D_HighBid</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>300</v>
       </c>
-      <c r="D2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>input_data/electriciteitsmix-2026-uur-data.csv</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>demand_quantity</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2D_ModerateBid</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>70</v>
       </c>
-      <c r="C3" t="s">
-        <v>15</v>
+      <c r="F3" t="n">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -712,48 +734,62 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA09FDC5-7B4D-4318-8065-B985F3D8846B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.90625" bestFit="1" customWidth="1"/>
+    <col width="14.1796875" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="13.90625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="8.81640625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="9.6328125" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="7.90625" bestFit="1" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Energy Capacity</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Power Capacity</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Efficiency</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Initial SOC</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>End SOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>2000</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>1000</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>0.9</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>0.5</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>0.5</v>
       </c>
     </row>
